--- a/data/common_project_data/indicators-master.xlsx
+++ b/data/common_project_data/indicators-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.crawshaw\projects\weca_regional_indicators\data\common_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8C90BBA-E53B-4491-814C-F1C677BA6A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB87CCCB-0B3C-4DEE-8966-E6CB0EFADCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,9 +589,6 @@
     <t>All</t>
   </si>
   <si>
-    <t>Mode share for all journeys</t>
-  </si>
-  <si>
     <t>DfT National Travel Survey</t>
   </si>
   <si>
@@ -2677,6 +2674,9 @@
   </si>
   <si>
     <t>£m</t>
+  </si>
+  <si>
+    <t>Mode share for active travel and public transport (all trip purposes)</t>
   </si>
 </sst>
 </file>
@@ -3536,42 +3536,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>608</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>611</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>614</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>616</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -9745,16 +9745,16 @@
         <v>37</v>
       </c>
       <c r="AM1" s="26" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AQ1" s="2"/>
     </row>
@@ -9874,16 +9874,16 @@
         <v>76</v>
       </c>
       <c r="AM2" s="27" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AN2" s="12" t="s">
         <v>77</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AP2" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AQ2" s="2"/>
     </row>
@@ -9907,13 +9907,13 @@
         <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>84</v>
@@ -9923,13 +9923,13 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="11" t="s">
         <v>726</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>727</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>113</v>
@@ -9938,10 +9938,10 @@
         <v>141</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="T3" s="23">
         <v>46133</v>
@@ -9950,19 +9950,19 @@
         <v>4</v>
       </c>
       <c r="W3" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>731</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>89</v>
@@ -9975,13 +9975,13 @@
         <v>91</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AM3" s="5">
         <v>3</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP3" s="1" t="b">
         <v>1</v>
@@ -10007,13 +10007,13 @@
         <v>94</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>95</v>
@@ -10023,16 +10023,16 @@
         <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>734</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>735</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="Q4" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>96</v>
@@ -10050,22 +10050,22 @@
         <v>98</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>739</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>89</v>
@@ -10081,7 +10081,7 @@
         <v>4</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP4" s="1" t="b">
         <v>1</v>
@@ -10107,16 +10107,16 @@
         <v>103</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L5" s="5">
         <v>2020</v>
@@ -10125,10 +10125,10 @@
         <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="O5" s="11" t="s">
         <v>742</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>743</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>105</v>
@@ -10143,28 +10143,28 @@
         <v>2023</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="U5" s="1">
         <v>16</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>746</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>89</v>
@@ -10180,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP5" s="1" t="b">
         <v>1</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="6" spans="1:43" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>79</v>
@@ -10203,10 +10203,10 @@
         <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -10215,20 +10215,20 @@
         <v>112</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>753</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="11" t="s">
         <v>755</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>756</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>105</v>
@@ -10249,19 +10249,19 @@
         <v>18</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>89</v>
@@ -10274,13 +10274,13 @@
         <v>110</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP6" s="1" t="b">
         <v>1</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="7" spans="1:43" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
@@ -10303,10 +10303,10 @@
         <v>111</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -10315,23 +10315,23 @@
         <v>112</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="11" t="s">
         <v>765</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>766</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>87</v>
@@ -10346,19 +10346,19 @@
         <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>89</v>
@@ -10371,13 +10371,13 @@
         <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AM7" s="5">
         <v>5</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AP7" s="1" t="b">
         <v>1</v>
@@ -10403,13 +10403,13 @@
         <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>118</v>
@@ -10425,13 +10425,13 @@
         <v>120</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>121</v>
@@ -10446,19 +10446,19 @@
         <v>18</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>89</v>
@@ -10474,7 +10474,7 @@
         <v>12</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP8" s="1" t="b">
         <v>0</v>
@@ -10497,26 +10497,26 @@
         <v>126</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>127</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>128</v>
@@ -10531,7 +10531,7 @@
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>88</v>
@@ -10547,13 +10547,13 @@
         <v>91</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AM9" s="5">
         <v>6</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP9" s="1" t="b">
         <v>1</v>
@@ -10579,47 +10579,47 @@
         <v>132</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
         <v>133</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="O10" s="11" t="s">
         <v>773</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>774</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="S10" s="24">
         <v>46054</v>
       </c>
       <c r="T10" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>779</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>134</v>
@@ -10641,7 +10641,7 @@
         <v>7</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP10" s="1" t="b">
         <v>0</v>
@@ -10719,7 +10719,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>148</v>
@@ -10757,7 +10757,7 @@
         <v>9</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP12" s="1" t="b">
         <v>1</v>
@@ -10786,7 +10786,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>156</v>
@@ -10830,7 +10830,7 @@
         <v>11</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP13" s="1" t="b">
         <v>1</v>
@@ -10852,97 +10852,97 @@
       <c r="E14" s="25">
         <v>2</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>166</v>
+      <c r="F14" t="s">
+        <v>859</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>121</v>
       </c>
       <c r="S14" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>789</v>
       </c>
       <c r="U14" s="1">
         <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG14" s="6"/>
       <c r="AH14" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AJ14" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AL14" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="AM14" s="5">
         <v>10</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP14" s="1" t="b">
         <v>1</v>
@@ -10950,7 +10950,7 @@
     </row>
     <row r="15" spans="1:43" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>163</v>
@@ -10959,62 +10959,62 @@
         <v>164</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="O15" s="11" t="s">
         <v>829</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>830</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>128</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>833</v>
       </c>
       <c r="U15" s="1">
         <v>9</v>
       </c>
       <c r="V15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>88</v>
@@ -11023,26 +11023,26 @@
         <v>89</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG15" s="6"/>
       <c r="AI15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AL15" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL15" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="AM15" s="5">
         <v>1</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP15" s="1" t="b">
         <v>1</v>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="16" spans="1:43" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>163</v>
@@ -11059,50 +11059,50 @@
         <v>164</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U16" s="1">
         <v>6</v>
       </c>
       <c r="V16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="Y16" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="Z16" s="1" t="s">
         <v>88</v>
@@ -11111,23 +11111,23 @@
         <v>89</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG16" s="6"/>
       <c r="AJ16" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AM16" s="5">
         <v>3</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP16" s="1" t="b">
         <v>1</v>
@@ -11135,7 +11135,7 @@
     </row>
     <row r="17" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>163</v>
@@ -11144,32 +11144,32 @@
         <v>164</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>96</v>
@@ -11181,7 +11181,7 @@
         <v>5</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Z17" s="1" t="s">
         <v>88</v>
@@ -11190,7 +11190,7 @@
         <v>89</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG17" s="6"/>
       <c r="AH17" s="1" t="s">
@@ -11200,19 +11200,19 @@
         <v>91</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AM17" s="5">
         <v>4</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP17" s="1" t="b">
         <v>1</v>
@@ -11220,7 +11220,7 @@
     </row>
     <row r="18" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>163</v>
@@ -11229,29 +11229,29 @@
         <v>164</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>87</v>
@@ -11260,7 +11260,7 @@
         <v>1</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z18" s="1" t="s">
         <v>88</v>
@@ -11269,17 +11269,17 @@
         <v>89</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG18" s="6"/>
       <c r="AL18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM18" s="5">
         <v>6</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP18" s="1" t="b">
         <v>1</v>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="19" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>163</v>
@@ -11296,32 +11296,32 @@
         <v>164</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>96</v>
@@ -11333,32 +11333,32 @@
         <v>4</v>
       </c>
       <c r="V19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y19" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="Z19" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AC19" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG19" s="6"/>
       <c r="AL19" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AM19" s="5">
         <v>5</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP19" s="1" t="b">
         <v>1</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="20" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>163</v>
@@ -11375,29 +11375,29 @@
         <v>164</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>96</v>
@@ -11409,7 +11409,7 @@
         <v>1</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z20" s="1" t="s">
         <v>88</v>
@@ -11418,26 +11418,26 @@
         <v>89</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG20" s="6"/>
       <c r="AI20" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AM20" s="5">
         <v>7</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AP20" s="1" t="b">
         <v>1</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="21" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>163</v>
@@ -11454,32 +11454,32 @@
         <v>164</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>148</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>96</v>
@@ -11491,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Z21" s="1" t="s">
         <v>88</v>
@@ -11500,17 +11500,17 @@
         <v>89</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG21" s="6"/>
       <c r="AL21" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM21" s="5">
         <v>8</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP21" s="1" t="b">
         <v>1</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="22" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>163</v>
@@ -11527,27 +11527,27 @@
         <v>164</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="5"/>
       <c r="Y22" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG22" s="6"/>
       <c r="AL22" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AM22" s="5">
         <v>2</v>
@@ -11558,7 +11558,7 @@
     </row>
     <row r="23" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>163</v>
@@ -11567,44 +11567,44 @@
         <v>164</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U23" s="1">
         <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z23" s="1" t="s">
         <v>88</v>
@@ -11613,17 +11613,17 @@
         <v>89</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG23" s="6"/>
       <c r="AL23" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AM23" s="5">
         <v>3</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP23" s="1" t="b">
         <v>1</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="24" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>163</v>
@@ -11640,57 +11640,57 @@
         <v>164</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="V24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y24" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="Z24" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG24" s="6"/>
       <c r="AL24" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AM24" s="5">
         <v>9</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP24" s="1" t="b">
         <v>0</v>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="25" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>163</v>
@@ -11707,19 +11707,19 @@
         <v>164</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="H25" s="1">
         <v>-1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L25" s="5"/>
       <c r="R25" s="1" t="s">
@@ -11732,29 +11732,29 @@
         <v>24</v>
       </c>
       <c r="V25" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y25" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="Y25" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="AF25" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG25" s="6"/>
       <c r="AJ25" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM25" s="5">
         <v>11</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP25" s="1" t="b">
         <v>0</v>
@@ -11762,28 +11762,28 @@
     </row>
     <row r="26" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="H26" s="1">
         <v>-1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L26" s="5"/>
       <c r="R26" s="1" t="s">
@@ -11796,23 +11796,23 @@
         <v>24</v>
       </c>
       <c r="V26" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y26" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="Y26" s="1" t="s">
+      <c r="AF26" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="AF26" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="AG26" s="6"/>
       <c r="AL26" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM26" s="5">
         <v>11</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP26" s="1" t="b">
         <v>1</v>
@@ -11820,38 +11820,38 @@
     </row>
     <row r="27" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="H27" s="1">
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>87</v>
@@ -11860,7 +11860,7 @@
         <v>2</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>88</v>
@@ -11869,20 +11869,20 @@
         <v>89</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG27" s="6"/>
       <c r="AI27" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AM27" s="5">
         <v>3</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP27" s="1" t="b">
         <v>1</v>
@@ -11890,38 +11890,38 @@
     </row>
     <row r="28" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H28" s="1">
         <v>-1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>113</v>
@@ -11936,7 +11936,7 @@
         <v>14</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Z28" s="1" t="s">
         <v>88</v>
@@ -11945,20 +11945,20 @@
         <v>89</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG28" s="6"/>
       <c r="AI28" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AL28" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="AL28" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="AM28" s="5">
         <v>2</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP28" s="1" t="b">
         <v>1</v>
@@ -11966,38 +11966,38 @@
     </row>
     <row r="29" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H29" s="1">
         <v>-1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>87</v>
@@ -12006,32 +12006,32 @@
         <v>1</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Z29" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AC29" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG29" s="6"/>
       <c r="AI29" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL29" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="AL29" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="AM29" s="5">
         <v>4</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP29" s="1" t="b">
         <v>0</v>
@@ -12039,38 +12039,38 @@
     </row>
     <row r="30" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>113</v>
@@ -12079,13 +12079,13 @@
         <v>96</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U30" s="1">
         <v>7</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z30" s="1" t="s">
         <v>88</v>
@@ -12094,14 +12094,14 @@
         <v>89</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG30" s="6"/>
       <c r="AI30" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AL30" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="AL30" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="AM30" s="5">
         <v>1</v>
@@ -12110,7 +12110,7 @@
         <v>91</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP30" s="1" t="b">
         <v>1</v>
@@ -12118,72 +12118,72 @@
     </row>
     <row r="31" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="H31" s="1">
         <v>-1</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U31" s="1">
         <v>6</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Z31" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AC31" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG31" s="6"/>
       <c r="AL31" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM31" s="5">
         <v>5</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP31" s="1" t="b">
         <v>1</v>
@@ -12191,22 +12191,22 @@
     </row>
     <row r="32" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H32" s="1">
         <v>-1</v>
@@ -12215,48 +12215,48 @@
         <v>112</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="U32" s="1">
         <v>6</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Z32" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AC32" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG32" s="6"/>
       <c r="AL32" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM32" s="5">
         <v>6</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AP32" s="1" t="b">
         <v>1</v>
@@ -12264,44 +12264,44 @@
     </row>
     <row r="33" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="H33" s="1">
         <v>-1</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U33" s="1">
         <v>6</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Z33" s="1" t="s">
         <v>88</v>
@@ -12310,20 +12310,20 @@
         <v>89</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG33" s="6"/>
       <c r="AI33" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AL33" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="AL33" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="AM33" s="5">
         <v>7</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP33" s="1" t="b">
         <v>1</v>
@@ -12331,47 +12331,47 @@
     </row>
     <row r="34" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U34" s="1">
         <v>6</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Z34" s="1" t="s">
         <v>88</v>
@@ -12380,17 +12380,17 @@
         <v>89</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG34" s="6"/>
       <c r="AL34" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM34" s="5">
         <v>8</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP34" s="1" t="b">
         <v>1</v>
@@ -12398,29 +12398,29 @@
     </row>
     <row r="35" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="5"/>
       <c r="Y35" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z35" s="1" t="s">
         <v>143</v>
@@ -12429,11 +12429,11 @@
         <v>89</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG35" s="6"/>
       <c r="AL35" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AM35" s="5">
         <v>9</v>
@@ -12444,19 +12444,19 @@
     </row>
     <row r="36" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>155</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="L36" s="5"/>
       <c r="R36" s="1" t="s">
@@ -12478,26 +12478,26 @@
         <v>9</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG36" s="6"/>
       <c r="AI36" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AM36" s="5">
         <v>10</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP36" s="1" t="b">
         <v>1</v>
@@ -12505,38 +12505,38 @@
     </row>
     <row r="37" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="H37" s="1">
         <v>-1</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>96</v>
@@ -12548,7 +12548,7 @@
         <v>4</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Z37" s="1" t="s">
         <v>88</v>
@@ -12557,17 +12557,17 @@
         <v>89</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG37" s="6"/>
       <c r="AL37" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM37" s="5">
         <v>1</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP37" s="1" t="b">
         <v>1</v>
@@ -12575,38 +12575,38 @@
     </row>
     <row r="38" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>96</v>
@@ -12618,7 +12618,7 @@
         <v>4</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Z38" s="1" t="s">
         <v>88</v>
@@ -12627,20 +12627,20 @@
         <v>89</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG38" s="6"/>
       <c r="AI38" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM38" s="5">
         <v>2</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP38" s="1" t="b">
         <v>1</v>
@@ -12648,50 +12648,50 @@
     </row>
     <row r="39" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U39" s="1">
         <v>4</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Z39" s="1" t="s">
         <v>88</v>
@@ -12700,17 +12700,17 @@
         <v>89</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG39" s="6"/>
       <c r="AL39" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AM39" s="5">
         <v>8</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP39" s="1" t="b">
         <v>1</v>
@@ -12718,32 +12718,32 @@
     </row>
     <row r="40" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>96</v>
@@ -12755,10 +12755,10 @@
         <v>4</v>
       </c>
       <c r="V40" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y40" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="Z40" s="1" t="s">
         <v>88</v>
@@ -12767,20 +12767,20 @@
         <v>89</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG40" s="6"/>
       <c r="AI40" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL40" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AM40" s="5">
         <v>9</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AP40" s="1" t="b">
         <v>1</v>
@@ -12788,47 +12788,47 @@
     </row>
     <row r="41" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J41" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U41" s="1">
         <v>3</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Z41" s="1" t="s">
         <v>88</v>
@@ -12837,20 +12837,20 @@
         <v>89</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG41" s="6"/>
       <c r="AI41" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL41" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AM41" s="5">
         <v>7</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP41" s="1" t="b">
         <v>1</v>
@@ -12858,47 +12858,47 @@
     </row>
     <row r="42" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="H42" s="1">
         <v>-1</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U42" s="1">
         <v>3</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Z42" s="1" t="s">
         <v>88</v>
@@ -12907,17 +12907,17 @@
         <v>89</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG42" s="6"/>
       <c r="AL42" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AM42" s="5">
         <v>6</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP42" s="1" t="b">
         <v>1</v>
@@ -12925,38 +12925,38 @@
     </row>
     <row r="43" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="H43" s="1">
         <v>-1</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J43" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>113</v>
@@ -12965,13 +12965,13 @@
         <v>96</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="U43" s="1">
         <v>10</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>88</v>
@@ -12980,20 +12980,20 @@
         <v>89</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG43" s="6"/>
       <c r="AI43" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AM43" s="5">
         <v>3</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP43" s="1" t="b">
         <v>1</v>
@@ -13001,57 +13001,57 @@
     </row>
     <row r="44" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="H44" s="1">
         <v>-1</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="L44" s="5"/>
       <c r="Y44" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z44" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG44" s="6"/>
       <c r="AI44" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AL44" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="AL44" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="AM44" s="5">
         <v>4</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP44" s="1" t="b">
         <v>1</v>
@@ -13059,34 +13059,34 @@
     </row>
     <row r="45" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="F45" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H45" s="1">
         <v>-1</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="1" t="s">
@@ -13105,7 +13105,7 @@
         <v>6</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>88</v>
@@ -13114,17 +13114,17 @@
         <v>89</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG45" s="6"/>
       <c r="AL45" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AM45" s="5">
         <v>5</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP45" s="1" t="b">
         <v>1</v>
@@ -13132,35 +13132,35 @@
     </row>
     <row r="46" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="H46" s="1">
         <v>-1</v>
       </c>
       <c r="J46" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>412</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>87</v>
@@ -13169,7 +13169,7 @@
         <v>1</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Z46" s="1" t="s">
         <v>88</v>
@@ -13178,11 +13178,11 @@
         <v>89</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG46" s="6"/>
       <c r="AL46" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AM46" s="5">
         <v>10</v>
@@ -13193,45 +13193,45 @@
     </row>
     <row r="47" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="H47" s="1">
         <v>-1</v>
       </c>
       <c r="L47" s="5"/>
       <c r="Y47" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Z47" s="1" t="s">
         <v>143</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AC47" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG47" s="6"/>
       <c r="AL47" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM47" s="5">
         <v>11</v>
@@ -13242,38 +13242,38 @@
     </row>
     <row r="48" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="C48" s="22" t="s">
-        <v>425</v>
-      </c>
       <c r="D48" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E48" s="22">
         <v>5</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H48" s="1">
         <v>-1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>128</v>
@@ -13288,38 +13288,38 @@
         <v>24</v>
       </c>
       <c r="V48" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="W48" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="W48" s="1" t="s">
+      <c r="Y48" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="Y48" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="Z48" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA48" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AB48" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="AB48" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="AC48" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF48" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG48" s="6"/>
       <c r="AL48" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AM48" s="5">
         <v>1</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP48" s="1" t="b">
         <v>1</v>
@@ -13327,44 +13327,44 @@
     </row>
     <row r="49" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>435</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D49" s="22" t="s">
+      <c r="E49" s="22" t="s">
         <v>436</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="F49" s="22" t="s">
+        <v>792</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>793</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="H49" s="1">
         <v>1</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>128</v>
@@ -13376,38 +13376,38 @@
         <v>24</v>
       </c>
       <c r="V49" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y49" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="W49" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="Z49" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA49" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AB49" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF49" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG49" s="6"/>
       <c r="AL49" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AM49" s="5">
         <v>10</v>
       </c>
       <c r="AO49" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP49" s="1" t="b">
         <v>1</v>
@@ -13415,53 +13415,53 @@
     </row>
     <row r="50" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="E50" s="22" t="s">
+      <c r="F50" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J50" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>128</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>96</v>
@@ -13473,38 +13473,38 @@
         <v>12</v>
       </c>
       <c r="V50" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y50" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="W50" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Y50" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="Z50" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AC50" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF50" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG50" s="6"/>
       <c r="AL50" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AM50" s="5">
         <v>9</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP50" s="1" t="b">
         <v>1</v>
@@ -13512,44 +13512,44 @@
     </row>
     <row r="51" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D51" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D51" s="22" t="s">
+      <c r="E51" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="F51" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="G51" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J51" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>128</v>
@@ -13561,41 +13561,41 @@
         <v>2</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Z51" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG51" s="6"/>
       <c r="AK51" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AL51" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="AL51" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="AM51" s="5">
         <v>8</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP51" s="1" t="b">
         <v>1</v>
@@ -13603,47 +13603,47 @@
     </row>
     <row r="52" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>469</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D52" s="22" t="s">
+      <c r="E52" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="F52" s="22" t="s">
         <v>471</v>
       </c>
-      <c r="F52" s="22" t="s">
+      <c r="G52" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="H52" s="1">
         <v>-1</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="O52" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="O52" s="11" t="s">
+      <c r="P52" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>96</v>
@@ -13652,38 +13652,38 @@
         <v>24</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Z52" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF52" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG52" s="6"/>
       <c r="AL52" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AM52" s="5">
         <v>2</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AP52" s="1" t="b">
         <v>1</v>
@@ -13691,37 +13691,37 @@
     </row>
     <row r="53" spans="1:42" ht="135" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>470</v>
-      </c>
-      <c r="E53" s="22" t="s">
+      <c r="F53" s="22" t="s">
+        <v>801</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>802</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="H53" s="1">
         <v>-1</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L53" s="5">
         <v>2020</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>96</v>
@@ -13730,41 +13730,41 @@
         <v>13</v>
       </c>
       <c r="V53" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="W53" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="W53" s="1" t="s">
+      <c r="Y53" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="Y53" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="Z53" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA53" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AC53" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF53" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG53" s="6"/>
       <c r="AI53" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="AL53" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="AL53" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="AM53" s="5">
         <v>3</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AP53" s="1" t="b">
         <v>1</v>
@@ -13772,78 +13772,78 @@
     </row>
     <row r="54" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>493</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D54" s="22" t="s">
+      <c r="E54" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="F54" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="F54" s="22" t="s">
+      <c r="G54" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="R54" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="U54" s="1">
         <v>24</v>
       </c>
       <c r="V54" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y54" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="W54" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Y54" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="Z54" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA54" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AC54" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF54" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG54" s="6"/>
       <c r="AK54" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="AL54" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="AL54" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="AM54" s="5">
         <v>7</v>
       </c>
       <c r="AO54" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP54" s="1" t="b">
         <v>1</v>
@@ -13851,22 +13851,22 @@
     </row>
     <row r="55" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="E55" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="E55" s="22" t="s">
+      <c r="F55" s="22" t="s">
         <v>508</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>509</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
@@ -13876,23 +13876,23 @@
       </c>
       <c r="L55" s="5"/>
       <c r="Y55" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Z55" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AC55" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF55" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG55" s="6"/>
       <c r="AL55" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AM55" s="5">
         <v>6</v>
@@ -13903,22 +13903,22 @@
     </row>
     <row r="56" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="E56" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="E56" s="22" t="s">
+      <c r="F56" s="22" t="s">
         <v>513</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>514</v>
       </c>
       <c r="H56" s="1">
         <v>1</v>
@@ -13928,23 +13928,23 @@
       </c>
       <c r="L56" s="5"/>
       <c r="Y56" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z56" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AA56" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AC56" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF56" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG56" s="6"/>
       <c r="AL56" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AM56" s="5">
         <v>5</v>
@@ -13955,47 +13955,47 @@
     </row>
     <row r="57" spans="1:42" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="E57" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="E57" s="22" t="s">
+      <c r="F57" s="22" t="s">
+        <v>800</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>801</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="O57" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="P57" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>96</v>
@@ -14004,38 +14004,38 @@
         <v>15</v>
       </c>
       <c r="V57" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="W57" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="W57" s="1" t="s">
+      <c r="Y57" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="Z57" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AA57" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AC57" s="1" t="s">
         <v>89</v>
       </c>
       <c r="AF57" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG57" s="6"/>
       <c r="AL57" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AM57" s="5">
         <v>4</v>
       </c>
       <c r="AO57" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP57" s="1" t="b">
         <v>1</v>
@@ -14043,50 +14043,50 @@
     </row>
     <row r="58" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H58" s="1">
         <v>-1</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U58" s="1">
         <v>3</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Z58" s="1" t="s">
         <v>88</v>
@@ -14095,14 +14095,14 @@
         <v>89</v>
       </c>
       <c r="AF58" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG58" s="6"/>
       <c r="AI58" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL58" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AM58" s="5">
         <v>1</v>
@@ -14111,7 +14111,7 @@
         <v>91</v>
       </c>
       <c r="AO58" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP58" s="1" t="b">
         <v>1</v>
@@ -14119,38 +14119,38 @@
     </row>
     <row r="59" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="H59" s="1">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J59" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>113</v>
@@ -14159,13 +14159,13 @@
         <v>96</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U59" s="1">
         <v>2</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Z59" s="1" t="s">
         <v>88</v>
@@ -14174,14 +14174,14 @@
         <v>89</v>
       </c>
       <c r="AF59" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG59" s="6"/>
       <c r="AI59" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL59" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM59" s="5">
         <v>5</v>
@@ -14190,7 +14190,7 @@
         <v>91</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP59" s="1" t="b">
         <v>1</v>
@@ -14198,41 +14198,41 @@
     </row>
     <row r="60" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="H60" s="1">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>113</v>
@@ -14247,7 +14247,7 @@
         <v>3</v>
       </c>
       <c r="Y60" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Z60" s="1" t="s">
         <v>88</v>
@@ -14256,20 +14256,20 @@
         <v>89</v>
       </c>
       <c r="AF60" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG60" s="6"/>
       <c r="AI60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM60" s="5">
         <v>8</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP60" s="1" t="b">
         <v>1</v>
@@ -14277,38 +14277,38 @@
     </row>
     <row r="61" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>555</v>
       </c>
       <c r="H61" s="1">
         <v>-1</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J61" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>113</v>
@@ -14323,7 +14323,7 @@
         <v>3</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>88</v>
@@ -14332,17 +14332,17 @@
         <v>89</v>
       </c>
       <c r="AF61" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG61" s="6"/>
       <c r="AL61" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AM61" s="5">
         <v>6</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP61" s="1" t="b">
         <v>1</v>
@@ -14350,38 +14350,38 @@
     </row>
     <row r="62" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>113</v>
@@ -14393,7 +14393,7 @@
         <v>12</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Z62" s="1" t="s">
         <v>88</v>
@@ -14402,17 +14402,17 @@
         <v>89</v>
       </c>
       <c r="AF62" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG62" s="6"/>
       <c r="AL62" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM62" s="5">
         <v>2</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP62" s="1" t="b">
         <v>1</v>
@@ -14420,38 +14420,38 @@
     </row>
     <row r="63" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="H63" s="1">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>113</v>
@@ -14463,7 +14463,7 @@
         <v>12</v>
       </c>
       <c r="Y63" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Z63" s="1" t="s">
         <v>88</v>
@@ -14472,17 +14472,17 @@
         <v>89</v>
       </c>
       <c r="AF63" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG63" s="6"/>
       <c r="AL63" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AM63" s="5">
         <v>3</v>
       </c>
       <c r="AO63" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP63" s="1" t="b">
         <v>1</v>
@@ -14490,22 +14490,22 @@
     </row>
     <row r="64" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="H64" s="1">
         <v>1</v>
@@ -14515,13 +14515,13 @@
       </c>
       <c r="L64" s="5"/>
       <c r="R64" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U64" s="1">
         <v>3</v>
       </c>
       <c r="Y64" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Z64" s="1" t="s">
         <v>143</v>
@@ -14530,7 +14530,7 @@
         <v>89</v>
       </c>
       <c r="AF64" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG64" s="6"/>
       <c r="AL64" s="1" t="s">
@@ -14545,22 +14545,22 @@
     </row>
     <row r="65" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="L65" s="5"/>
       <c r="Y65" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Z65" s="1" t="s">
         <v>143</v>
@@ -14579,7 +14579,7 @@
         <v>89</v>
       </c>
       <c r="AF65" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG65" s="6"/>
       <c r="AL65" s="1" t="s">
@@ -14594,38 +14594,38 @@
     </row>
     <row r="66" spans="1:42" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="H66" s="1">
         <v>-1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="V66" s="1" t="s">
+      <c r="Y66" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="Y66" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="Z66" s="1" t="s">
         <v>88</v>
@@ -14634,17 +14634,17 @@
         <v>89</v>
       </c>
       <c r="AF66" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG66" s="6"/>
       <c r="AL66" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AM66" s="5">
         <v>10</v>
       </c>
       <c r="AO66" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP66" s="1" t="b">
         <v>1</v>
@@ -14652,32 +14652,32 @@
     </row>
     <row r="67" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="H67" s="1">
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>113</v>
@@ -14692,7 +14692,7 @@
         <v>12</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Z67" s="1" t="s">
         <v>88</v>
@@ -14701,20 +14701,20 @@
         <v>89</v>
       </c>
       <c r="AF67" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG67" s="6"/>
       <c r="AI67" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AM67" s="5">
         <v>11</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AP67" s="1" t="b">
         <v>1</v>
@@ -14722,38 +14722,38 @@
     </row>
     <row r="68" spans="1:42" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J68" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>113</v>
@@ -14768,7 +14768,7 @@
         <v>36</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Z68" s="1" t="s">
         <v>88</v>
@@ -14777,20 +14777,20 @@
         <v>89</v>
       </c>
       <c r="AF68" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG68" s="6"/>
       <c r="AI68" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AM68" s="5">
         <v>4</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP68" s="1" t="b">
         <v>1</v>
@@ -14798,38 +14798,38 @@
     </row>
     <row r="69" spans="1:42" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="H69" s="1">
         <v>-1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>113</v>
@@ -14844,7 +14844,7 @@
         <v>12</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Z69" s="1" t="s">
         <v>88</v>
@@ -14853,17 +14853,17 @@
         <v>89</v>
       </c>
       <c r="AF69" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG69" s="6"/>
       <c r="AL69" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AM69" s="5">
         <v>7</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AP69" s="1" t="b">
         <v>1</v>
@@ -15105,78 +15105,78 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="B2" t="s">
         <v>619</v>
-      </c>
-      <c r="B2" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="B3" t="s">
         <v>621</v>
-      </c>
-      <c r="B3" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4" t="s">
         <v>623</v>
-      </c>
-      <c r="B4" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6" t="s">
         <v>625</v>
-      </c>
-      <c r="B6" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="B7" t="s">
         <v>627</v>
-      </c>
-      <c r="B7" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>841</v>
+      </c>
+      <c r="B10" t="s">
         <v>842</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>843</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>844</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>845</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>846</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>847</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>848</v>
-      </c>
-      <c r="H10" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -15204,63 +15204,63 @@
   <sheetData>
     <row r="1" spans="1:5" ht="298.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B4" t="s">
         <v>631</v>
-      </c>
-      <c r="B4" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="B5" t="s">
         <v>633</v>
-      </c>
-      <c r="B5" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B6" t="s">
         <v>635</v>
-      </c>
-      <c r="B6" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="B7" t="s">
         <v>637</v>
-      </c>
-      <c r="B7" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>642</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>643</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>37</v>
@@ -15274,13 +15274,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
+        <v>643</v>
+      </c>
+      <c r="D11" t="s">
         <v>644</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>645</v>
-      </c>
-      <c r="E11" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -15291,13 +15291,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>646</v>
+      </c>
+      <c r="D12" t="s">
+        <v>644</v>
+      </c>
+      <c r="E12" t="s">
         <v>647</v>
-      </c>
-      <c r="D12" t="s">
-        <v>645</v>
-      </c>
-      <c r="E12" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -15308,13 +15308,13 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
+        <v>648</v>
+      </c>
+      <c r="D13" t="s">
+        <v>644</v>
+      </c>
+      <c r="E13" t="s">
         <v>649</v>
-      </c>
-      <c r="D13" t="s">
-        <v>645</v>
-      </c>
-      <c r="E13" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -15325,13 +15325,13 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D14" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E14" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -15342,13 +15342,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>651</v>
+      </c>
+      <c r="D15" t="s">
+        <v>644</v>
+      </c>
+      <c r="E15" t="s">
         <v>652</v>
-      </c>
-      <c r="D15" t="s">
-        <v>645</v>
-      </c>
-      <c r="E15" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -15359,13 +15359,13 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
+        <v>653</v>
+      </c>
+      <c r="D16" t="s">
+        <v>644</v>
+      </c>
+      <c r="E16" t="s">
         <v>654</v>
-      </c>
-      <c r="D16" t="s">
-        <v>645</v>
-      </c>
-      <c r="E16" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15376,13 +15376,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D17" t="s">
+        <v>655</v>
+      </c>
+      <c r="E17" t="s">
         <v>656</v>
-      </c>
-      <c r="E17" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -15393,13 +15393,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
+        <v>657</v>
+      </c>
+      <c r="D18" t="s">
+        <v>655</v>
+      </c>
+      <c r="E18" t="s">
         <v>658</v>
-      </c>
-      <c r="D18" t="s">
-        <v>656</v>
-      </c>
-      <c r="E18" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -15410,13 +15410,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>659</v>
+      </c>
+      <c r="D19" t="s">
+        <v>655</v>
+      </c>
+      <c r="E19" t="s">
         <v>660</v>
-      </c>
-      <c r="D19" t="s">
-        <v>656</v>
-      </c>
-      <c r="E19" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -15427,13 +15427,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -15444,13 +15444,13 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D21" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -15461,13 +15461,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D22" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -15478,13 +15478,13 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D23" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E23" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -15495,13 +15495,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D24" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E24" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -15512,13 +15512,13 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D25" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E25" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -15529,13 +15529,13 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D26" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -15546,13 +15546,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D27" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -15563,13 +15563,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D28" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E28" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -15580,13 +15580,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D29" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E29" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -15597,13 +15597,13 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D30" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E30" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -15614,13 +15614,13 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D31" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E31" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -15631,13 +15631,13 @@
         <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D32" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E32" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -15648,13 +15648,13 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D33" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E33" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -15665,13 +15665,13 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D34" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E34" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -15682,13 +15682,13 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D35" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -15699,13 +15699,13 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D36" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E36" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -15716,13 +15716,13 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D37" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E37" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -15733,13 +15733,13 @@
         <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D38" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E38" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -15750,13 +15750,13 @@
         <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D39" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E39" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -15767,13 +15767,13 @@
         <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D40" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E40" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -15784,13 +15784,13 @@
         <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E41" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -15801,13 +15801,13 @@
         <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D42" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E42" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -15818,13 +15818,13 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
+        <v>684</v>
+      </c>
+      <c r="D43" t="s">
+        <v>655</v>
+      </c>
+      <c r="E43" t="s">
         <v>685</v>
-      </c>
-      <c r="D43" t="s">
-        <v>656</v>
-      </c>
-      <c r="E43" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -15835,13 +15835,13 @@
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D44" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E44" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -15852,13 +15852,13 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D45" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E45" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -15869,13 +15869,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D46" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E46" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -15886,13 +15886,13 @@
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D47" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E47" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -15903,13 +15903,13 @@
         <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D48" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E48" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -15920,69 +15920,69 @@
         <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D49" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E49" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B52" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B53" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B54" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B55" t="s">
         <v>697</v>
-      </c>
-      <c r="B55" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="C58" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="D58" s="13" t="s">
         <v>642</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>643</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>37</v>
@@ -15990,19 +15990,19 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B59" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C59" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D59" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E59" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -16010,141 +16010,141 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C60" t="s">
+        <v>643</v>
+      </c>
+      <c r="D60" t="s">
         <v>644</v>
       </c>
-      <c r="D60" t="s">
-        <v>645</v>
-      </c>
       <c r="E60" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B61" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C61" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D61" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E61" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B62" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C62" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D62" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E62" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B63" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C63" t="s">
+        <v>703</v>
+      </c>
+      <c r="D63" t="s">
+        <v>644</v>
+      </c>
+      <c r="E63" t="s">
         <v>704</v>
-      </c>
-      <c r="D63" t="s">
-        <v>645</v>
-      </c>
-      <c r="E63" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B64" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C64" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D64" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E64" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="B71" t="s">
         <v>711</v>
-      </c>
-      <c r="B71" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B72" t="s">
         <v>713</v>
-      </c>
-      <c r="B72" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B73" t="s">
         <v>715</v>
-      </c>
-      <c r="B73" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="B74" t="s">
         <v>717</v>
-      </c>
-      <c r="B74" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -16152,7 +16152,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -16160,7 +16160,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -16168,7 +16168,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -16176,7 +16176,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -16184,7 +16184,7 @@
         <v>5</v>
       </c>
       <c r="B81" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -16193,27 +16193,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B67AE13FBD584ABEFCF026840CED6F" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11ebdf7d5c906124ef40ef85c2b08d8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d56b9130-d22a-480d-bb83-f34040f04d96" xmlns:ns3="dd8606a3-d959-45f7-996e-3c98d970357c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="395e369db30c2620103728840cc29626" ns2:_="" ns3:_="">
     <xsd:import namespace="d56b9130-d22a-480d-bb83-f34040f04d96"/>
@@ -16482,10 +16461,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d56b9130-d22a-480d-bb83-f34040f04d96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="d56b9130-d22a-480d-bb83-f34040f04d96" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd8606a3-d959-45f7-996e-3c98d970357c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
+    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16508,20 +16519,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E038410E-E6A9-42FC-B223-5F20C9C2E8EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4B7956-BCA0-46CA-BF6B-C7215DA15D81}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d56b9130-d22a-480d-bb83-f34040f04d96"/>
-    <ds:schemaRef ds:uri="dd8606a3-d959-45f7-996e-3c98d970357c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>